--- a/cases/00_防护用例/测试数据.xlsx
+++ b/cases/00_防护用例/测试数据.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品目录" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市销售" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +461,16 @@
           <t>客户数</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>销售额_A</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>销售额_B</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -486,6 +497,12 @@
       <c r="F2" t="n">
         <v>15</v>
       </c>
+      <c r="G2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,6 +529,12 @@
       <c r="F3" t="n">
         <v>20</v>
       </c>
+      <c r="G3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1800</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -538,6 +561,12 @@
       <c r="F4" t="n">
         <v>10</v>
       </c>
+      <c r="G4" t="n">
+        <v>800</v>
+      </c>
+      <c r="H4" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -564,6 +593,12 @@
       <c r="F5" t="n">
         <v>12</v>
       </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -590,6 +625,12 @@
       <c r="F6" t="n">
         <v>8</v>
       </c>
+      <c r="G6" t="n">
+        <v>900</v>
+      </c>
+      <c r="H6" t="n">
+        <v>900</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -616,6 +657,12 @@
       <c r="F7" t="n">
         <v>10</v>
       </c>
+      <c r="G7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -642,6 +689,12 @@
       <c r="F8" t="n">
         <v>6</v>
       </c>
+      <c r="G8" t="n">
+        <v>600</v>
+      </c>
+      <c r="H8" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -668,6 +721,12 @@
       <c r="F9" t="n">
         <v>7</v>
       </c>
+      <c r="G9" t="n">
+        <v>700</v>
+      </c>
+      <c r="H9" t="n">
+        <v>700</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -694,6 +753,12 @@
       <c r="F10" t="n">
         <v>18</v>
       </c>
+      <c r="G10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -720,6 +785,12 @@
       <c r="F11" t="n">
         <v>25</v>
       </c>
+      <c r="G11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -746,6 +817,12 @@
       <c r="F12" t="n">
         <v>5</v>
       </c>
+      <c r="G12" t="n">
+        <v>500</v>
+      </c>
+      <c r="H12" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -771,6 +848,12 @@
       </c>
       <c r="F13" t="n">
         <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>650</v>
+      </c>
+      <c r="H13" t="n">
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -837,4 +920,139 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>销量</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>深圳市</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C3" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>珠海市</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>800</v>
+      </c>
+      <c r="C4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>佛山市</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>东莞市</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>中山市</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>700</v>
+      </c>
+      <c r="C7" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>惠州市</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>950</v>
+      </c>
+      <c r="C8" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>江门市</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>650</v>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/cases/00_防护用例/测试数据.xlsx
+++ b/cases/00_防护用例/测试数据.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,11 @@
           <t>销售额_B</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>报告图片</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -503,6 +508,11 @@
       <c r="H2" t="n">
         <v>1200</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -535,6 +545,11 @@
       <c r="H3" t="n">
         <v>1800</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,6 +582,11 @@
       <c r="H4" t="n">
         <v>800</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -599,6 +619,11 @@
       <c r="H5" t="n">
         <v>1000</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,6 +656,11 @@
       <c r="H6" t="n">
         <v>900</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -663,6 +693,11 @@
       <c r="H7" t="n">
         <v>1100</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -695,6 +730,11 @@
       <c r="H8" t="n">
         <v>600</v>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -727,6 +767,11 @@
       <c r="H9" t="n">
         <v>700</v>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -759,6 +804,11 @@
       <c r="H10" t="n">
         <v>1500</v>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -791,6 +841,11 @@
       <c r="H11" t="n">
         <v>2000</v>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -823,6 +878,11 @@
       <c r="H12" t="n">
         <v>500</v>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -854,6 +914,11 @@
       </c>
       <c r="H13" t="n">
         <v>650</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>_test_image.png</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cases/00_防护用例/测试数据.xlsx
+++ b/cases/00_防护用例/测试数据.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品目录" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市销售" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基站分布" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +474,11 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>运营商</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>报告图片</t>
         </is>
       </c>
@@ -510,6 +516,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -547,6 +558,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -584,6 +600,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -621,6 +642,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -658,6 +684,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -695,6 +726,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -732,6 +768,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -769,6 +810,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -806,6 +852,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -843,6 +894,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -880,6 +936,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>_test_image.png</t>
         </is>
       </c>
@@ -916,6 +977,11 @@
         <v>650</v>
       </c>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>_test_image.png</t>
         </is>
@@ -1120,4 +1186,403 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>站点名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>运营商</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>经度</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>纬度</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>用户数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>流量GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>北京朝阳站</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>116.4551</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.945</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G2" t="n">
+        <v>350.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>北京海淀站</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>116.298</v>
+      </c>
+      <c r="E3" t="n">
+        <v>39.959</v>
+      </c>
+      <c r="F3" t="n">
+        <v>980</v>
+      </c>
+      <c r="G3" t="n">
+        <v>280.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>上海浦东站</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>121.544</v>
+      </c>
+      <c r="E4" t="n">
+        <v>31.2209</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1580</v>
+      </c>
+      <c r="G4" t="n">
+        <v>420.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>上海徐汇站</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>121.437</v>
+      </c>
+      <c r="E5" t="n">
+        <v>31.184</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>310.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>广州天河站</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>113.361</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23.124</v>
+      </c>
+      <c r="F6" t="n">
+        <v>980</v>
+      </c>
+      <c r="G6" t="n">
+        <v>280.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>深圳南山站</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>113.93</v>
+      </c>
+      <c r="E7" t="n">
+        <v>22.533</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1340</v>
+      </c>
+      <c r="G7" t="n">
+        <v>390.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>成都武侯站</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>104.043</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30.642</v>
+      </c>
+      <c r="F8" t="n">
+        <v>760</v>
+      </c>
+      <c r="G8" t="n">
+        <v>210.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>武汉洪山站</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>华中</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>114.344</v>
+      </c>
+      <c r="E9" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>890</v>
+      </c>
+      <c r="G9" t="n">
+        <v>245.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>杭州西湖站</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>120.15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G10" t="n">
+        <v>310.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>西安雁塔站</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>108.947</v>
+      </c>
+      <c r="E11" t="n">
+        <v>34.23</v>
+      </c>
+      <c r="F11" t="n">
+        <v>650</v>
+      </c>
+      <c r="G11" t="n">
+        <v>180.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>南京鼓楼站</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>118.77</v>
+      </c>
+      <c r="E12" t="n">
+        <v>32.066</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1020</v>
+      </c>
+      <c r="G12" t="n">
+        <v>290.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>重庆渝北站</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>106.631</v>
+      </c>
+      <c r="E13" t="n">
+        <v>29.718</v>
+      </c>
+      <c r="F13" t="n">
+        <v>870</v>
+      </c>
+      <c r="G13" t="n">
+        <v>240.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/cases/00_防护用例/测试数据.xlsx
+++ b/cases/00_防护用例/测试数据.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品目录" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城市销售" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基站分布" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网络KPI" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,15 +33,21 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -54,14 +61,34 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1194,7 +1221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1582,6 +1609,1655 @@
         <v>240.1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>杭州西湖站</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>120.15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G14" t="n">
+        <v>380.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>南京鼓楼站</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>118.78</v>
+      </c>
+      <c r="E15" t="n">
+        <v>32.06</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G15" t="n">
+        <v>305.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>武汉洪山站</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>华中</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>114.34</v>
+      </c>
+      <c r="E16" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G16" t="n">
+        <v>295.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>长沙岳麓站</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>华中</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>112.94</v>
+      </c>
+      <c r="E17" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="F17" t="n">
+        <v>890</v>
+      </c>
+      <c r="G17" t="n">
+        <v>245.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>重庆渝北站</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>106.63</v>
+      </c>
+      <c r="E18" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G18" t="n">
+        <v>360.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>西安雁塔站</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>108.93</v>
+      </c>
+      <c r="E19" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="F19" t="n">
+        <v>780</v>
+      </c>
+      <c r="G19" t="n">
+        <v>215.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>沈阳和平站</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>东北</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>123.43</v>
+      </c>
+      <c r="E20" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="F20" t="n">
+        <v>920</v>
+      </c>
+      <c r="G20" t="n">
+        <v>255.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>哈尔滨南岗站</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>东北</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>126.66</v>
+      </c>
+      <c r="E21" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="F21" t="n">
+        <v>750</v>
+      </c>
+      <c r="G21" t="n">
+        <v>208.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>郑州金水站</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>华中</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>113.66</v>
+      </c>
+      <c r="E22" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G22" t="n">
+        <v>318.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>济南历下站</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>117.02</v>
+      </c>
+      <c r="E23" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1020</v>
+      </c>
+      <c r="G23" t="n">
+        <v>282.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>南昌东湖站</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>115.89</v>
+      </c>
+      <c r="E24" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="F24" t="n">
+        <v>830</v>
+      </c>
+      <c r="G24" t="n">
+        <v>230.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>福州鼓楼站</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="F25" t="n">
+        <v>870</v>
+      </c>
+      <c r="G25" t="n">
+        <v>242.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>昆明盘龙站</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>102.83</v>
+      </c>
+      <c r="E26" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="F26" t="n">
+        <v>690</v>
+      </c>
+      <c r="G26" t="n">
+        <v>192.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>基站名称</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>运营商</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>RSRP均值</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>RSRQ均值</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>接通率</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>掉线率</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>丢包率</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>时延ms</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>带宽利用率</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>用户数</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>流量GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>北京朝阳站</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>-85</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>350.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>北京朝阳站</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>-83</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1280</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>365.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>北京朝阳站</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-82</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1320</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>390.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>上海浦东站</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-80</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1580</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>420.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>上海浦东站</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-79</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1620</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>445.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>上海浦东站</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-78</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-7</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1680</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>470.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>广州天河站</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-88</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>980</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>280.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>广州天河站</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-86</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>1010</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>295.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>广州天河站</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-85</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>310.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>深圳南山站</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-84</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>1340</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>390.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>深圳南山站</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-82</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>1380</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>410.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>深圳南山站</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>联通</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-81</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>1420</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>435.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>成都武侯站</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>760</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>210.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>成都武侯站</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-88</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>790</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>225.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>成都武侯站</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>电信</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-87</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>820</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>240.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>杭州西湖站</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-82</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>380.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>杭州西湖站</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-80</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>1490</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>405.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>杭州西湖站</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-79</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>1530</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>430.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>武汉洪山站</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>华中</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-87</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>1080</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>295.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>武汉洪山站</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>华中</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-85</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>1120</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>315.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>武汉洪山站</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>华中</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-84</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>1160</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>335.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>重庆渝北站</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-86</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>1320</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>360.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>重庆渝北站</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-84</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>1360</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>385.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>重庆渝北站</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>西部</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-83</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>410.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
